--- a/uploads/friday schedule.xlsx
+++ b/uploads/friday schedule.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86873EC3-8582-40FF-98E9-241F6CD27953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE8F2C6-AB65-49FD-925F-91F42F2BFBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="93">
   <si>
     <t>Names</t>
   </si>
@@ -33,21 +44,288 @@
     <t>Group Number</t>
   </si>
   <si>
+    <t>Talmage Kay</t>
+  </si>
+  <si>
+    <t>Michael Fusselman</t>
+  </si>
+  <si>
+    <t>Sydney Adams</t>
+  </si>
+  <si>
+    <t>Rebekah Johnson</t>
+  </si>
+  <si>
+    <t>Brynna Morris</t>
+  </si>
+  <si>
+    <t>Anette Lara</t>
+  </si>
+  <si>
+    <t>Yoyo Brown</t>
+  </si>
+  <si>
+    <t>Spencer Helsley</t>
+  </si>
+  <si>
+    <t>Ole Warndahl</t>
+  </si>
+  <si>
+    <t>Hailey Hogue</t>
+  </si>
+  <si>
+    <t>Valery Chavez Cahuana</t>
+  </si>
+  <si>
+    <t>Carson Davis</t>
+  </si>
+  <si>
+    <t>Keaton Bellum</t>
+  </si>
+  <si>
+    <t>Corrin Christensen</t>
+  </si>
+  <si>
+    <t>Emily Lease</t>
+  </si>
+  <si>
+    <t>Manuel Abreu Ramirez</t>
+  </si>
+  <si>
+    <t>Grace Dioquino</t>
+  </si>
+  <si>
+    <t>Katherine Burgoyne</t>
+  </si>
+  <si>
+    <t>Amaela Kersee</t>
+  </si>
+  <si>
+    <t>Saleena Christopherson</t>
+  </si>
+  <si>
+    <t>Belle Terribilini</t>
+  </si>
+  <si>
+    <t>Kate Van Haaften</t>
+  </si>
+  <si>
+    <t>Regina Hardman</t>
+  </si>
+  <si>
+    <t>Rebecca Rust</t>
+  </si>
+  <si>
+    <t>Madeline Pulsipher</t>
+  </si>
+  <si>
+    <t>Kirarahu Williams</t>
+  </si>
+  <si>
+    <t>Brigham Conlin</t>
+  </si>
+  <si>
+    <t>Griffin Bischoff</t>
+  </si>
+  <si>
+    <t>Kelly Byers</t>
+  </si>
+  <si>
+    <t>Glenda Malidadi</t>
+  </si>
+  <si>
+    <t>Lili Lozano Olguin</t>
+  </si>
+  <si>
+    <t>Westley Bledsoe</t>
+  </si>
+  <si>
+    <t>Yasmin Akhtar</t>
+  </si>
+  <si>
+    <t>Sibayo Ntshalintshali</t>
+  </si>
+  <si>
+    <t>Cassi Bloomfield</t>
+  </si>
+  <si>
+    <t>Emma Erickson</t>
+  </si>
+  <si>
+    <t>Jayton Lakey</t>
+  </si>
+  <si>
+    <t>Shainah (Chris) Dioquino</t>
+  </si>
+  <si>
+    <t>Daniel Hakisimana</t>
+  </si>
+  <si>
+    <t>Fabrice Andre</t>
+  </si>
+  <si>
+    <t>Carly Valdivieso</t>
+  </si>
+  <si>
+    <t>Jacob Gonzalez</t>
+  </si>
+  <si>
+    <t>Mikayla Belknap</t>
+  </si>
+  <si>
+    <t>Ruby Danielson</t>
+  </si>
+  <si>
+    <t>Abbie Collinwood</t>
+  </si>
+  <si>
+    <t>Delaney Lawrence</t>
+  </si>
+  <si>
+    <t>Mary Meline</t>
+  </si>
+  <si>
+    <t>Andrew Benge</t>
+  </si>
+  <si>
+    <t>Ashlyn Danielson</t>
+  </si>
+  <si>
+    <t>Sophia Lind</t>
+  </si>
+  <si>
+    <t>Nolan Bradford</t>
+  </si>
+  <si>
+    <t>Milena Lima</t>
+  </si>
+  <si>
+    <t>Nathan Otey</t>
+  </si>
+  <si>
+    <t>Vivian Winkelman</t>
+  </si>
+  <si>
+    <t>Emma Weber</t>
+  </si>
+  <si>
+    <t>Lucia Alliaud Bennet</t>
+  </si>
+  <si>
+    <t>Robyn Kingsford</t>
+  </si>
+  <si>
+    <t>Emma Addington</t>
+  </si>
+  <si>
+    <t>Jenna Moore</t>
+  </si>
+  <si>
+    <t>Kailey Baysinger</t>
+  </si>
+  <si>
+    <t>Aliah Bresler</t>
+  </si>
+  <si>
+    <t>Sara Turner</t>
+  </si>
+  <si>
+    <t>Andrew Parrella</t>
+  </si>
+  <si>
+    <t>Katelyn Wilhoit</t>
+  </si>
+  <si>
+    <t>Kennedy Brady</t>
+  </si>
+  <si>
+    <t>Gloria Gao</t>
+  </si>
+  <si>
+    <t>Izy Faustini</t>
+  </si>
+  <si>
+    <t>Jo Kilpack</t>
+  </si>
+  <si>
+    <t>Julio Astorga</t>
+  </si>
+  <si>
+    <t>Katie Clark</t>
+  </si>
+  <si>
+    <t>Marie Semadeni</t>
+  </si>
+  <si>
+    <t>Tess Burrell</t>
+  </si>
+  <si>
+    <t>Sam Gutty</t>
+  </si>
+  <si>
+    <t>Devanee Smith</t>
+  </si>
+  <si>
+    <t>Attend training in the Taylor Chapel</t>
+  </si>
+  <si>
+    <t>Lunch
+1 PM - 1:30 PM</t>
+  </si>
+  <si>
+    <t>Eat lunch</t>
+  </si>
+  <si>
+    <t>Walk Your Schedule Tours
+2:00 PM - 5:00 PM</t>
+  </si>
+  <si>
     <t>Training
-12:00 pm - 1 pm</t>
-  </si>
-  <si>
-    <t>Talmage Kay</t>
-  </si>
-  <si>
-    <t>Attend training</t>
+12:00 PM - 1:00 PM</t>
+  </si>
+  <si>
+    <t>Give tours to students</t>
+  </si>
+  <si>
+    <t>Kylie Jones</t>
+  </si>
+  <si>
+    <t>Rachel Stansbury</t>
+  </si>
+  <si>
+    <t>Miriam Allen</t>
+  </si>
+  <si>
+    <t>Rachel Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annika Mickelsen </t>
+  </si>
+  <si>
+    <t>Check students into tours</t>
+  </si>
+  <si>
+    <t>Take 4 people to do your thing in the quad. You're awesome, Manny!!</t>
+  </si>
+  <si>
+    <t>Pair students for tours</t>
+  </si>
+  <si>
+    <t>Bouncy</t>
+  </si>
+  <si>
+    <t>Clean-up
+5:00 PM - 5:15 PM</t>
+  </si>
+  <si>
+    <t>Clean up tours and put into Taylor 120.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,13 +333,76 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,17 +417,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FFFF99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -361,13 +727,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
     <col min="2" max="2" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -375,18 +742,1440 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>12</v>
+      </c>
+      <c r="C27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" t="s">
+        <v>78</v>
+      </c>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="F40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" t="s">
+        <v>76</v>
+      </c>
+      <c r="D44" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F46" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47" t="s">
+        <v>78</v>
+      </c>
+      <c r="E47" t="s">
+        <v>81</v>
+      </c>
+      <c r="F47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" t="s">
+        <v>78</v>
+      </c>
+      <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" t="s">
+        <v>78</v>
+      </c>
+      <c r="E49" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" t="s">
+        <v>76</v>
+      </c>
+      <c r="D50" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" t="s">
+        <v>81</v>
+      </c>
+      <c r="F50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" t="s">
+        <v>81</v>
+      </c>
+      <c r="F51" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" t="s">
+        <v>81</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" t="s">
+        <v>76</v>
+      </c>
+      <c r="D53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53" t="s">
+        <v>81</v>
+      </c>
+      <c r="F53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" t="s">
+        <v>81</v>
+      </c>
+      <c r="F54" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" t="s">
+        <v>81</v>
+      </c>
+      <c r="F55" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" t="s">
+        <v>81</v>
+      </c>
+      <c r="F57" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" t="s">
+        <v>81</v>
+      </c>
+      <c r="F58" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" t="s">
+        <v>81</v>
+      </c>
+      <c r="F60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D63" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" t="s">
+        <v>81</v>
+      </c>
+      <c r="F63" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" t="s">
+        <v>76</v>
+      </c>
+      <c r="D64" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" t="s">
+        <v>81</v>
+      </c>
+      <c r="F65" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" t="s">
+        <v>81</v>
+      </c>
+      <c r="F66" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" t="s">
+        <v>81</v>
+      </c>
+      <c r="F67" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" t="s">
+        <v>81</v>
+      </c>
+      <c r="F68" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" t="s">
+        <v>81</v>
+      </c>
+      <c r="F69" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" t="s">
+        <v>81</v>
+      </c>
+      <c r="F70" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" t="s">
+        <v>81</v>
+      </c>
+      <c r="F73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74" t="s">
+        <v>78</v>
+      </c>
+      <c r="E74" t="s">
+        <v>81</v>
+      </c>
+      <c r="F74" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>76</v>
+      </c>
+      <c r="D75" t="s">
+        <v>78</v>
+      </c>
+      <c r="E75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76" t="s">
+        <v>78</v>
+      </c>
+      <c r="E76" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77" t="s">
+        <v>78</v>
+      </c>
+      <c r="E77" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78" t="s">
+        <v>78</v>
+      </c>
+      <c r="E78" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" t="s">
+        <v>76</v>
+      </c>
+      <c r="D79" t="s">
+        <v>78</v>
+      </c>
+      <c r="E79" t="s">
+        <v>87</v>
+      </c>
+      <c r="F79" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" t="s">
+        <v>76</v>
+      </c>
+      <c r="D80" t="s">
+        <v>78</v>
+      </c>
+      <c r="E80" t="s">
+        <v>87</v>
+      </c>
+      <c r="F80" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/friday schedule.xlsx
+++ b/uploads/friday schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE8F2C6-AB65-49FD-925F-91F42F2BFBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822827D6-58D8-4A19-AAA8-B47D65D4A1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="115">
   <si>
     <t>Names</t>
   </si>
@@ -318,7 +318,79 @@
 5:00 PM - 5:15 PM</t>
   </si>
   <si>
-    <t>Clean up tours and put into Taylor 120.</t>
+    <t>Kalob DeVries</t>
+  </si>
+  <si>
+    <t>Cassi DeVries</t>
+  </si>
+  <si>
+    <t>Prepare
+8:00 AM - 11:30 AM</t>
+  </si>
+  <si>
+    <t>Pick up truck and set up.</t>
+  </si>
+  <si>
+    <t>Pick up Kainoa's
+11:30 AM - 12:30 PM</t>
+  </si>
+  <si>
+    <t>Set up lunch
+12:30 PM - 1:00 PM</t>
+  </si>
+  <si>
+    <t>set up lunch</t>
+  </si>
+  <si>
+    <t>Pick up food</t>
+  </si>
+  <si>
+    <t>Prepare for RM night
+4:30 PM - 5:00 PM</t>
+  </si>
+  <si>
+    <t>Pick up Jimmy Johns</t>
+  </si>
+  <si>
+    <t>Give Training</t>
+  </si>
+  <si>
+    <t>Help lead clean up efforts</t>
+  </si>
+  <si>
+    <t>RM Night
+5:30 PM - 7:30 PM</t>
+  </si>
+  <si>
+    <t>Run RM night checkins</t>
+  </si>
+  <si>
+    <t>Go to RM night for checkins</t>
+  </si>
+  <si>
+    <t>Help at RM night</t>
+  </si>
+  <si>
+    <t>Get food at some point</t>
+  </si>
+  <si>
+    <t>Clean-up
+7:30 PM</t>
+  </si>
+  <si>
+    <t>Clean up RM night and go home</t>
+  </si>
+  <si>
+    <t>Pick up truck and set up. Balloon arches</t>
+  </si>
+  <si>
+    <t>Pick up truck and set up. WYST</t>
+  </si>
+  <si>
+    <t>Clean up tours and put into Taylor 120. Once everything is done, you may go home.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decorate for RM night. Remember the BYU I letters </t>
   </si>
 </sst>
 </file>
@@ -428,10 +500,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -727,14 +799,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="2" max="5" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="87" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -742,1440 +814,1552 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="K1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
       <c r="F2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" t="s">
-        <v>81</v>
-      </c>
       <c r="F3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>81</v>
-      </c>
       <c r="F4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>81</v>
-      </c>
       <c r="F5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>81</v>
-      </c>
       <c r="F6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>81</v>
-      </c>
       <c r="F7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>81</v>
-      </c>
       <c r="F8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>81</v>
-      </c>
       <c r="F9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B10">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" t="s">
-        <v>81</v>
-      </c>
       <c r="F10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B11">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
       <c r="F11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>81</v>
-      </c>
       <c r="F12" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" t="s">
-        <v>81</v>
-      </c>
       <c r="F13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <v>16</v>
       </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" t="s">
-        <v>81</v>
-      </c>
       <c r="F14" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <v>16</v>
       </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" t="s">
-        <v>81</v>
-      </c>
       <c r="F15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
         <v>88</v>
       </c>
-      <c r="F16" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
-      <c r="C17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
       <c r="F17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B18">
         <v>5</v>
       </c>
-      <c r="C18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>81</v>
-      </c>
       <c r="F18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" t="s">
+        <v>81</v>
+      </c>
+      <c r="J18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>81</v>
-      </c>
       <c r="F19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B20">
         <v>14</v>
       </c>
-      <c r="C20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" t="s">
-        <v>81</v>
-      </c>
       <c r="F20" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>81</v>
+      </c>
+      <c r="J20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B21">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" t="s">
-        <v>81</v>
-      </c>
       <c r="F21" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B22">
         <v>17</v>
       </c>
-      <c r="C22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" t="s">
-        <v>81</v>
-      </c>
       <c r="F22" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>81</v>
+      </c>
+      <c r="J22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B23">
         <v>8</v>
       </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" t="s">
-        <v>81</v>
-      </c>
       <c r="F23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G23" t="s">
+        <v>78</v>
+      </c>
+      <c r="H23" t="s">
+        <v>81</v>
+      </c>
+      <c r="J23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B24">
         <v>7</v>
       </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>81</v>
-      </c>
       <c r="F24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" t="s">
+        <v>81</v>
+      </c>
+      <c r="J24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B25">
         <v>7</v>
       </c>
-      <c r="C25" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
       <c r="F25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" t="s">
+        <v>81</v>
+      </c>
+      <c r="J25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B26">
         <v>12</v>
       </c>
-      <c r="C26" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
       <c r="F26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J26" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B27">
         <v>12</v>
       </c>
-      <c r="C27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" t="s">
-        <v>81</v>
-      </c>
       <c r="F27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B28">
         <v>9</v>
       </c>
-      <c r="C28" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
       <c r="F28" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" t="s">
+        <v>81</v>
+      </c>
+      <c r="J28" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B29">
         <v>18</v>
       </c>
-      <c r="C29" t="s">
-        <v>76</v>
-      </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
       <c r="F29" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G29" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" t="s">
+        <v>81</v>
+      </c>
+      <c r="J29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B30">
         <v>11</v>
       </c>
-      <c r="C30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
       <c r="F30" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s">
+        <v>78</v>
+      </c>
+      <c r="H30" t="s">
+        <v>81</v>
+      </c>
+      <c r="J30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B31">
         <v>11</v>
       </c>
-      <c r="C31" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
       <c r="F31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B32">
         <v>10</v>
       </c>
-      <c r="C32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D32" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
       <c r="F32" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G32" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" t="s">
+        <v>81</v>
+      </c>
+      <c r="J32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C33" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" t="s">
-        <v>81</v>
-      </c>
       <c r="F33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" t="s">
+        <v>81</v>
+      </c>
+      <c r="J33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
       <c r="F34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J34" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C35" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" t="s">
-        <v>81</v>
-      </c>
       <c r="F35" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G35" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" t="s">
+        <v>81</v>
+      </c>
+      <c r="J35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" t="s">
-        <v>81</v>
-      </c>
       <c r="F36" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s">
+        <v>81</v>
+      </c>
+      <c r="J36" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C37" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" t="s">
-        <v>78</v>
-      </c>
-      <c r="E37" t="s">
-        <v>81</v>
-      </c>
       <c r="F37" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s">
+        <v>81</v>
+      </c>
+      <c r="J37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C38" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38" t="s">
-        <v>81</v>
-      </c>
       <c r="F38" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G38" t="s">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s">
+        <v>81</v>
+      </c>
+      <c r="J38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" t="s">
-        <v>81</v>
-      </c>
       <c r="F39" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G39" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" t="s">
+        <v>81</v>
+      </c>
+      <c r="J39" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" t="s">
-        <v>81</v>
-      </c>
       <c r="F40" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G40" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" t="s">
-        <v>81</v>
-      </c>
       <c r="F41" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G41" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s">
+        <v>81</v>
+      </c>
+      <c r="J41" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C42" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" t="s">
-        <v>81</v>
-      </c>
       <c r="F42" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G42" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" t="s">
+        <v>81</v>
+      </c>
+      <c r="J42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C43" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" t="s">
-        <v>78</v>
-      </c>
-      <c r="E43" t="s">
-        <v>81</v>
-      </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G43" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s">
+        <v>81</v>
+      </c>
+      <c r="J43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C44" t="s">
-        <v>76</v>
-      </c>
-      <c r="D44" t="s">
-        <v>78</v>
-      </c>
-      <c r="E44" t="s">
-        <v>81</v>
-      </c>
       <c r="F44" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s">
+        <v>81</v>
+      </c>
+      <c r="J44" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C45" t="s">
-        <v>76</v>
-      </c>
-      <c r="D45" t="s">
-        <v>78</v>
-      </c>
-      <c r="E45" t="s">
-        <v>81</v>
-      </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G45" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" t="s">
+        <v>81</v>
+      </c>
+      <c r="J45" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C46" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" t="s">
-        <v>78</v>
-      </c>
-      <c r="E46" t="s">
-        <v>81</v>
-      </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s">
+        <v>81</v>
+      </c>
+      <c r="J46" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C47" t="s">
-        <v>76</v>
-      </c>
-      <c r="D47" t="s">
-        <v>78</v>
-      </c>
-      <c r="E47" t="s">
-        <v>81</v>
-      </c>
       <c r="F47" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G47" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" t="s">
+        <v>81</v>
+      </c>
+      <c r="J47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" t="s">
-        <v>78</v>
-      </c>
-      <c r="E48" t="s">
-        <v>81</v>
-      </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G48" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" t="s">
+        <v>81</v>
+      </c>
+      <c r="J48" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C49" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" t="s">
-        <v>81</v>
-      </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G49" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" t="s">
+        <v>81</v>
+      </c>
+      <c r="J49" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C50" t="s">
-        <v>76</v>
-      </c>
-      <c r="D50" t="s">
-        <v>78</v>
-      </c>
-      <c r="E50" t="s">
-        <v>81</v>
-      </c>
       <c r="F50" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G50" t="s">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s">
+        <v>81</v>
+      </c>
+      <c r="J50" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C51" t="s">
-        <v>76</v>
-      </c>
-      <c r="D51" t="s">
-        <v>78</v>
-      </c>
-      <c r="E51" t="s">
-        <v>81</v>
-      </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G51" t="s">
+        <v>78</v>
+      </c>
+      <c r="H51" t="s">
+        <v>81</v>
+      </c>
+      <c r="J51" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C52" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52" t="s">
-        <v>81</v>
-      </c>
       <c r="F52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G52" t="s">
+        <v>78</v>
+      </c>
+      <c r="H52" t="s">
+        <v>81</v>
+      </c>
+      <c r="J52" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C53" t="s">
-        <v>76</v>
-      </c>
-      <c r="D53" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53" t="s">
-        <v>81</v>
-      </c>
       <c r="F53" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s">
+        <v>81</v>
+      </c>
+      <c r="J53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C54" t="s">
-        <v>76</v>
-      </c>
-      <c r="D54" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54" t="s">
-        <v>81</v>
-      </c>
       <c r="F54" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G54" t="s">
+        <v>78</v>
+      </c>
+      <c r="H54" t="s">
+        <v>81</v>
+      </c>
+      <c r="J54" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C55" t="s">
-        <v>76</v>
-      </c>
-      <c r="D55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55" t="s">
-        <v>81</v>
-      </c>
       <c r="F55" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G55" t="s">
+        <v>78</v>
+      </c>
+      <c r="H55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" t="s">
-        <v>78</v>
-      </c>
-      <c r="E56" t="s">
-        <v>81</v>
-      </c>
       <c r="F56" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s">
+        <v>78</v>
+      </c>
+      <c r="H56" t="s">
+        <v>81</v>
+      </c>
+      <c r="J56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C57" t="s">
-        <v>76</v>
-      </c>
-      <c r="D57" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" t="s">
-        <v>81</v>
-      </c>
       <c r="F57" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s">
+        <v>78</v>
+      </c>
+      <c r="H57" t="s">
+        <v>81</v>
+      </c>
+      <c r="J57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C58" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" t="s">
-        <v>81</v>
-      </c>
       <c r="F58" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s">
+        <v>78</v>
+      </c>
+      <c r="H58" t="s">
+        <v>81</v>
+      </c>
+      <c r="J58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C59" t="s">
-        <v>76</v>
-      </c>
-      <c r="D59" t="s">
-        <v>78</v>
-      </c>
-      <c r="E59" t="s">
-        <v>81</v>
-      </c>
       <c r="F59" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G59" t="s">
+        <v>78</v>
+      </c>
+      <c r="H59" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C60" t="s">
-        <v>76</v>
-      </c>
-      <c r="D60" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" t="s">
-        <v>81</v>
-      </c>
       <c r="F60" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G60" t="s">
+        <v>78</v>
+      </c>
+      <c r="H60" t="s">
+        <v>81</v>
+      </c>
+      <c r="J60" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C61" t="s">
-        <v>76</v>
-      </c>
-      <c r="D61" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" t="s">
-        <v>81</v>
-      </c>
       <c r="F61" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s">
+        <v>78</v>
+      </c>
+      <c r="H61" t="s">
+        <v>81</v>
+      </c>
+      <c r="J61" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C62" t="s">
-        <v>76</v>
-      </c>
-      <c r="D62" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" t="s">
-        <v>81</v>
-      </c>
       <c r="F62" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s">
+        <v>78</v>
+      </c>
+      <c r="H62" t="s">
+        <v>81</v>
+      </c>
+      <c r="J62" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C63" t="s">
-        <v>76</v>
-      </c>
-      <c r="D63" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" t="s">
-        <v>81</v>
-      </c>
       <c r="F63" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s">
+        <v>78</v>
+      </c>
+      <c r="H63" t="s">
+        <v>81</v>
+      </c>
+      <c r="J63" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C64" t="s">
-        <v>76</v>
-      </c>
-      <c r="D64" t="s">
-        <v>78</v>
-      </c>
-      <c r="E64" t="s">
-        <v>81</v>
-      </c>
       <c r="F64" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s">
+        <v>78</v>
+      </c>
+      <c r="H64" t="s">
+        <v>81</v>
+      </c>
+      <c r="J64" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C65" t="s">
-        <v>76</v>
-      </c>
-      <c r="D65" t="s">
-        <v>78</v>
-      </c>
-      <c r="E65" t="s">
-        <v>81</v>
-      </c>
       <c r="F65" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s">
+        <v>78</v>
+      </c>
+      <c r="H65" t="s">
+        <v>81</v>
+      </c>
+      <c r="J65" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C66" t="s">
-        <v>76</v>
-      </c>
-      <c r="D66" t="s">
-        <v>78</v>
-      </c>
-      <c r="E66" t="s">
-        <v>81</v>
-      </c>
       <c r="F66" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s">
+        <v>78</v>
+      </c>
+      <c r="H66" t="s">
+        <v>81</v>
+      </c>
+      <c r="J66" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C67" t="s">
-        <v>76</v>
-      </c>
-      <c r="D67" t="s">
-        <v>78</v>
-      </c>
-      <c r="E67" t="s">
-        <v>81</v>
-      </c>
       <c r="F67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G67" t="s">
+        <v>78</v>
+      </c>
+      <c r="H67" t="s">
+        <v>81</v>
+      </c>
+      <c r="J67" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C68" t="s">
-        <v>76</v>
-      </c>
-      <c r="D68" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" t="s">
-        <v>81</v>
-      </c>
       <c r="F68" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s">
+        <v>78</v>
+      </c>
+      <c r="H68" t="s">
+        <v>81</v>
+      </c>
+      <c r="J68" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C69" t="s">
-        <v>76</v>
-      </c>
-      <c r="D69" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" t="s">
-        <v>81</v>
-      </c>
       <c r="F69" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s">
+        <v>78</v>
+      </c>
+      <c r="H69" t="s">
+        <v>81</v>
+      </c>
+      <c r="J69" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C70" t="s">
-        <v>76</v>
-      </c>
-      <c r="D70" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" t="s">
-        <v>81</v>
-      </c>
       <c r="F70" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s">
+        <v>78</v>
+      </c>
+      <c r="H70" t="s">
+        <v>81</v>
+      </c>
+      <c r="J70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C71" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" t="s">
-        <v>81</v>
-      </c>
       <c r="F71" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C72" t="s">
-        <v>76</v>
-      </c>
-      <c r="D72" t="s">
-        <v>78</v>
-      </c>
-      <c r="E72" t="s">
-        <v>81</v>
-      </c>
       <c r="F72" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s">
+        <v>78</v>
+      </c>
+      <c r="H72" t="s">
+        <v>81</v>
+      </c>
+      <c r="J72" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C73" t="s">
-        <v>76</v>
-      </c>
-      <c r="D73" t="s">
-        <v>78</v>
-      </c>
-      <c r="E73" t="s">
-        <v>81</v>
-      </c>
       <c r="F73" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s">
+        <v>78</v>
+      </c>
+      <c r="H73" t="s">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="s">
-        <v>76</v>
-      </c>
-      <c r="D74" t="s">
-        <v>78</v>
-      </c>
-      <c r="E74" t="s">
-        <v>81</v>
-      </c>
       <c r="F74" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
-      </c>
-      <c r="D75" t="s">
-        <v>78</v>
-      </c>
-      <c r="E75" t="s">
+        <v>112</v>
+      </c>
+      <c r="F75" t="s">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I75" t="s">
+        <v>108</v>
+      </c>
+      <c r="J75" t="s">
+        <v>103</v>
+      </c>
+      <c r="K75" t="s">
+        <v>107</v>
+      </c>
+      <c r="L75" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E76" t="s">
+        <v>98</v>
+      </c>
+      <c r="G76" t="s">
+        <v>78</v>
+      </c>
+      <c r="H76" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I76" t="s">
+        <v>114</v>
+      </c>
+      <c r="K76" t="s">
+        <v>107</v>
+      </c>
+      <c r="L76" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
         <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="D77" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E77" t="s">
+        <v>98</v>
+      </c>
+      <c r="G77" t="s">
+        <v>78</v>
+      </c>
+      <c r="H77" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I77" t="s">
+        <v>114</v>
+      </c>
+      <c r="K77" t="s">
+        <v>105</v>
+      </c>
+      <c r="L77" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
-      </c>
-      <c r="D78" t="s">
-        <v>78</v>
-      </c>
-      <c r="E78" t="s">
+        <v>111</v>
+      </c>
+      <c r="F78" t="s">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s">
+        <v>78</v>
+      </c>
+      <c r="H78" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I78" t="s">
+        <v>108</v>
+      </c>
+      <c r="J78" t="s">
+        <v>106</v>
+      </c>
+      <c r="K78" t="s">
+        <v>105</v>
+      </c>
+      <c r="L78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C79" t="s">
-        <v>76</v>
-      </c>
-      <c r="D79" t="s">
-        <v>78</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s">
         <v>87</v>
       </c>
-      <c r="F79" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J79" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C80" t="s">
-        <v>76</v>
-      </c>
-      <c r="D80" t="s">
-        <v>78</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
+        <v>76</v>
+      </c>
+      <c r="G80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s">
         <v>87</v>
       </c>
-      <c r="F80" t="s">
+      <c r="J80" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A81" s="12" t="s">
         <v>92</v>
+      </c>
+      <c r="I81" t="s">
+        <v>101</v>
+      </c>
+      <c r="K81" t="s">
+        <v>107</v>
+      </c>
+      <c r="L81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A82" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82" t="s">
+        <v>95</v>
+      </c>
+      <c r="F82" t="s">
+        <v>102</v>
+      </c>
+      <c r="I82" t="s">
+        <v>108</v>
+      </c>
+      <c r="K82" t="s">
+        <v>107</v>
+      </c>
+      <c r="L82" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/friday schedule.xlsx
+++ b/uploads/friday schedule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkay38\Documents\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822827D6-58D8-4A19-AAA8-B47D65D4A1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2DBE66-5436-4097-9A42-2D4BC62BEB2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="128">
   <si>
     <t>Names</t>
   </si>
@@ -314,10 +314,6 @@
     <t>Bouncy</t>
   </si>
   <si>
-    <t>Clean-up
-5:00 PM - 5:15 PM</t>
-  </si>
-  <si>
     <t>Kalob DeVries</t>
   </si>
   <si>
@@ -391,6 +387,50 @@
   </si>
   <si>
     <t xml:space="preserve">Decorate for RM night. Remember the BYU I letters </t>
+  </si>
+  <si>
+    <t>Nate Watson</t>
+  </si>
+  <si>
+    <t>Stephanie Colvin</t>
+  </si>
+  <si>
+    <t>Ruth Lauti</t>
+  </si>
+  <si>
+    <t>Kimball Benson</t>
+  </si>
+  <si>
+    <t>Chris Gomm</t>
+  </si>
+  <si>
+    <t>Joey Bennett</t>
+  </si>
+  <si>
+    <t>Sam Brubaker</t>
+  </si>
+  <si>
+    <t>Taylor Chapel</t>
+  </si>
+  <si>
+    <t>Taylor Cultural Hall</t>
+  </si>
+  <si>
+    <t>Dinner at MC Ballrooms</t>
+  </si>
+  <si>
+    <t>Clean-up tours
+5:00 PM - 5:15 PM</t>
+  </si>
+  <si>
+    <t>RM Night
+6:00 PM - 7:30 PM</t>
+  </si>
+  <si>
+    <t>MC Ballrooms</t>
+  </si>
+  <si>
+    <t>Go home</t>
   </si>
 </sst>
 </file>
@@ -421,7 +461,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,6 +516,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -489,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -513,6 +559,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,14 +846,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L82"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M89"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="5" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="5" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="87" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -814,13 +861,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>80</v>
@@ -832,19 +879,22 @@
         <v>79</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -861,10 +911,10 @@
         <v>81</v>
       </c>
       <c r="J2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -881,10 +931,10 @@
         <v>81</v>
       </c>
       <c r="J3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -901,10 +951,10 @@
         <v>81</v>
       </c>
       <c r="J4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -921,10 +971,10 @@
         <v>81</v>
       </c>
       <c r="J5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -941,10 +991,10 @@
         <v>81</v>
       </c>
       <c r="J6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -961,10 +1011,10 @@
         <v>81</v>
       </c>
       <c r="J7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
@@ -981,10 +1031,10 @@
         <v>81</v>
       </c>
       <c r="J8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -1001,10 +1051,10 @@
         <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>11</v>
       </c>
@@ -1021,10 +1071,10 @@
         <v>81</v>
       </c>
       <c r="J10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -1041,10 +1091,10 @@
         <v>81</v>
       </c>
       <c r="J11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>13</v>
       </c>
@@ -1061,10 +1111,10 @@
         <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>14</v>
       </c>
@@ -1081,10 +1131,10 @@
         <v>81</v>
       </c>
       <c r="J13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>15</v>
       </c>
@@ -1101,10 +1151,10 @@
         <v>81</v>
       </c>
       <c r="J14" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>16</v>
       </c>
@@ -1121,10 +1171,10 @@
         <v>81</v>
       </c>
       <c r="J15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
@@ -1141,10 +1191,10 @@
         <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>18</v>
       </c>
@@ -1161,10 +1211,10 @@
         <v>81</v>
       </c>
       <c r="J17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>19</v>
       </c>
@@ -1181,10 +1231,10 @@
         <v>81</v>
       </c>
       <c r="J18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>20</v>
       </c>
@@ -1201,10 +1251,10 @@
         <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>21</v>
       </c>
@@ -1221,10 +1271,10 @@
         <v>81</v>
       </c>
       <c r="J20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>22</v>
       </c>
@@ -1241,10 +1291,10 @@
         <v>81</v>
       </c>
       <c r="J21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>23</v>
       </c>
@@ -1261,10 +1311,10 @@
         <v>81</v>
       </c>
       <c r="J22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1281,10 +1331,10 @@
         <v>81</v>
       </c>
       <c r="J23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1301,10 +1351,10 @@
         <v>81</v>
       </c>
       <c r="J24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>26</v>
       </c>
@@ -1321,10 +1371,10 @@
         <v>81</v>
       </c>
       <c r="J25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>27</v>
       </c>
@@ -1341,10 +1391,10 @@
         <v>81</v>
       </c>
       <c r="J26" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>28</v>
       </c>
@@ -1361,10 +1411,10 @@
         <v>81</v>
       </c>
       <c r="J27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>29</v>
       </c>
@@ -1381,10 +1431,10 @@
         <v>81</v>
       </c>
       <c r="J28" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>30</v>
       </c>
@@ -1401,10 +1451,10 @@
         <v>81</v>
       </c>
       <c r="J29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>31</v>
       </c>
@@ -1421,10 +1471,10 @@
         <v>81</v>
       </c>
       <c r="J30" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>32</v>
       </c>
@@ -1441,10 +1491,10 @@
         <v>81</v>
       </c>
       <c r="J31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>33</v>
       </c>
@@ -1461,10 +1511,10 @@
         <v>81</v>
       </c>
       <c r="J32" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>34</v>
       </c>
@@ -1478,10 +1528,10 @@
         <v>81</v>
       </c>
       <c r="J33" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>35</v>
       </c>
@@ -1495,10 +1545,10 @@
         <v>81</v>
       </c>
       <c r="J34" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>36</v>
       </c>
@@ -1512,10 +1562,10 @@
         <v>81</v>
       </c>
       <c r="J35" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>37</v>
       </c>
@@ -1529,10 +1579,10 @@
         <v>81</v>
       </c>
       <c r="J36" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>38</v>
       </c>
@@ -1546,10 +1596,10 @@
         <v>81</v>
       </c>
       <c r="J37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>39</v>
       </c>
@@ -1563,10 +1613,10 @@
         <v>81</v>
       </c>
       <c r="J38" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>40</v>
       </c>
@@ -1580,10 +1630,10 @@
         <v>81</v>
       </c>
       <c r="J39" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>41</v>
       </c>
@@ -1597,10 +1647,10 @@
         <v>81</v>
       </c>
       <c r="J40" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>42</v>
       </c>
@@ -1614,10 +1664,10 @@
         <v>81</v>
       </c>
       <c r="J41" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>43</v>
       </c>
@@ -1631,10 +1681,10 @@
         <v>81</v>
       </c>
       <c r="J42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>44</v>
       </c>
@@ -1648,10 +1698,10 @@
         <v>81</v>
       </c>
       <c r="J43" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>45</v>
       </c>
@@ -1665,10 +1715,10 @@
         <v>81</v>
       </c>
       <c r="J44" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>46</v>
       </c>
@@ -1682,10 +1732,10 @@
         <v>81</v>
       </c>
       <c r="J45" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>47</v>
       </c>
@@ -1699,10 +1749,10 @@
         <v>81</v>
       </c>
       <c r="J46" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>48</v>
       </c>
@@ -1716,10 +1766,10 @@
         <v>81</v>
       </c>
       <c r="J47" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>49</v>
       </c>
@@ -1733,10 +1783,10 @@
         <v>81</v>
       </c>
       <c r="J48" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>50</v>
       </c>
@@ -1750,10 +1800,10 @@
         <v>81</v>
       </c>
       <c r="J49" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>51</v>
       </c>
@@ -1767,10 +1817,10 @@
         <v>81</v>
       </c>
       <c r="J50" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>52</v>
       </c>
@@ -1784,10 +1834,10 @@
         <v>81</v>
       </c>
       <c r="J51" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
@@ -1801,10 +1851,10 @@
         <v>81</v>
       </c>
       <c r="J52" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>54</v>
       </c>
@@ -1818,10 +1868,10 @@
         <v>81</v>
       </c>
       <c r="J53" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>55</v>
       </c>
@@ -1835,10 +1885,10 @@
         <v>81</v>
       </c>
       <c r="J54" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
@@ -1852,10 +1902,10 @@
         <v>81</v>
       </c>
       <c r="J55" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>57</v>
       </c>
@@ -1869,10 +1919,10 @@
         <v>81</v>
       </c>
       <c r="J56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>58</v>
       </c>
@@ -1886,10 +1936,10 @@
         <v>81</v>
       </c>
       <c r="J57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>59</v>
       </c>
@@ -1903,10 +1953,10 @@
         <v>81</v>
       </c>
       <c r="J58" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>60</v>
       </c>
@@ -1920,10 +1970,10 @@
         <v>81</v>
       </c>
       <c r="J59" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>61</v>
       </c>
@@ -1937,10 +1987,10 @@
         <v>81</v>
       </c>
       <c r="J60" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
@@ -1954,10 +2004,10 @@
         <v>81</v>
       </c>
       <c r="J61" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>63</v>
       </c>
@@ -1971,10 +2021,10 @@
         <v>81</v>
       </c>
       <c r="J62" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>64</v>
       </c>
@@ -1988,10 +2038,10 @@
         <v>81</v>
       </c>
       <c r="J63" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>65</v>
       </c>
@@ -2005,10 +2055,10 @@
         <v>81</v>
       </c>
       <c r="J64" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>66</v>
       </c>
@@ -2022,10 +2072,10 @@
         <v>81</v>
       </c>
       <c r="J65" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>67</v>
       </c>
@@ -2039,10 +2089,10 @@
         <v>81</v>
       </c>
       <c r="J66" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>68</v>
       </c>
@@ -2056,10 +2106,10 @@
         <v>81</v>
       </c>
       <c r="J67" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>69</v>
       </c>
@@ -2073,10 +2123,10 @@
         <v>81</v>
       </c>
       <c r="J68" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>70</v>
       </c>
@@ -2090,10 +2140,10 @@
         <v>81</v>
       </c>
       <c r="J69" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>71</v>
       </c>
@@ -2107,10 +2157,10 @@
         <v>81</v>
       </c>
       <c r="J70" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>72</v>
       </c>
@@ -2124,10 +2174,10 @@
         <v>81</v>
       </c>
       <c r="J71" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>73</v>
       </c>
@@ -2141,10 +2191,10 @@
         <v>81</v>
       </c>
       <c r="J72" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>74</v>
       </c>
@@ -2158,10 +2208,10 @@
         <v>81</v>
       </c>
       <c r="J73" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>75</v>
       </c>
@@ -2175,15 +2225,15 @@
         <v>81</v>
       </c>
       <c r="J74" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F75" t="s">
         <v>76</v>
@@ -2195,30 +2245,30 @@
         <v>87</v>
       </c>
       <c r="I75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K75" t="s">
-        <v>107</v>
-      </c>
-      <c r="L75" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+      <c r="M75" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G76" t="s">
         <v>78</v>
@@ -2227,27 +2277,27 @@
         <v>90</v>
       </c>
       <c r="I76" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K76" t="s">
-        <v>107</v>
-      </c>
-      <c r="L76" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+      <c r="M76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D77" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G77" t="s">
         <v>78</v>
@@ -2256,21 +2306,21 @@
         <v>90</v>
       </c>
       <c r="I77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K77" t="s">
-        <v>105</v>
-      </c>
-      <c r="L77" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="M77" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F78" t="s">
         <v>76</v>
@@ -2282,19 +2332,19 @@
         <v>89</v>
       </c>
       <c r="I78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K78" t="s">
-        <v>105</v>
-      </c>
-      <c r="L78" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="M78" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>85</v>
       </c>
@@ -2308,10 +2358,10 @@
         <v>87</v>
       </c>
       <c r="J79" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>86</v>
       </c>
@@ -2325,41 +2375,202 @@
         <v>87</v>
       </c>
       <c r="J80" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" t="s">
+        <v>100</v>
+      </c>
+      <c r="K81" t="s">
+        <v>106</v>
+      </c>
+      <c r="M81" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="I81" t="s">
+      <c r="C82" t="s">
+        <v>94</v>
+      </c>
+      <c r="F82" t="s">
         <v>101</v>
       </c>
-      <c r="K81" t="s">
+      <c r="I82" t="s">
         <v>107</v>
       </c>
-      <c r="L81" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A82" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C82" t="s">
-        <v>95</v>
-      </c>
-      <c r="F82" t="s">
-        <v>102</v>
-      </c>
-      <c r="I82" t="s">
-        <v>108</v>
-      </c>
       <c r="K82" t="s">
-        <v>107</v>
-      </c>
-      <c r="L82" t="s">
-        <v>110</v>
+        <v>106</v>
+      </c>
+      <c r="M82" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F83" t="s">
+        <v>121</v>
+      </c>
+      <c r="G83" t="s">
+        <v>122</v>
+      </c>
+      <c r="H83" t="s">
+        <v>122</v>
+      </c>
+      <c r="J83" t="s">
+        <v>123</v>
+      </c>
+      <c r="L83" t="s">
+        <v>126</v>
+      </c>
+      <c r="M83" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F84" t="s">
+        <v>121</v>
+      </c>
+      <c r="G84" t="s">
+        <v>122</v>
+      </c>
+      <c r="H84" t="s">
+        <v>122</v>
+      </c>
+      <c r="J84" t="s">
+        <v>123</v>
+      </c>
+      <c r="L84" t="s">
+        <v>126</v>
+      </c>
+      <c r="M84" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F85" t="s">
+        <v>121</v>
+      </c>
+      <c r="G85" t="s">
+        <v>122</v>
+      </c>
+      <c r="H85" t="s">
+        <v>122</v>
+      </c>
+      <c r="J85" t="s">
+        <v>123</v>
+      </c>
+      <c r="L85" t="s">
+        <v>126</v>
+      </c>
+      <c r="M85" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F86" t="s">
+        <v>121</v>
+      </c>
+      <c r="G86" t="s">
+        <v>122</v>
+      </c>
+      <c r="H86" t="s">
+        <v>122</v>
+      </c>
+      <c r="J86" t="s">
+        <v>123</v>
+      </c>
+      <c r="L86" t="s">
+        <v>126</v>
+      </c>
+      <c r="M86" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" t="s">
+        <v>121</v>
+      </c>
+      <c r="G87" t="s">
+        <v>122</v>
+      </c>
+      <c r="H87" t="s">
+        <v>122</v>
+      </c>
+      <c r="J87" t="s">
+        <v>123</v>
+      </c>
+      <c r="L87" t="s">
+        <v>126</v>
+      </c>
+      <c r="M87" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F88" t="s">
+        <v>121</v>
+      </c>
+      <c r="G88" t="s">
+        <v>122</v>
+      </c>
+      <c r="H88" t="s">
+        <v>122</v>
+      </c>
+      <c r="J88" t="s">
+        <v>123</v>
+      </c>
+      <c r="L88" t="s">
+        <v>126</v>
+      </c>
+      <c r="M88" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F89" t="s">
+        <v>121</v>
+      </c>
+      <c r="G89" t="s">
+        <v>122</v>
+      </c>
+      <c r="H89" t="s">
+        <v>122</v>
+      </c>
+      <c r="J89" t="s">
+        <v>123</v>
+      </c>
+      <c r="L89" t="s">
+        <v>126</v>
+      </c>
+      <c r="M89" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
